--- a/site/ADP-Workforce-Now-Okta-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-Okta-Integration-Guide/headings.xlsx
@@ -617,7 +617,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Applications</t>
+          <t>Connections</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
